--- a/test_samples/APL/sample1_ref.xlsx
+++ b/test_samples/APL/sample1_ref.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\APL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼sample\## 印尼 TOP 15 間 sample\14-APL LOGISTICS___VAT OK\$ 14-APL_____ OK VAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC06B7C2-95F9-4FEB-815E-3E88D2E7BA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6D541A-1C44-4202-8C91-CFB01699D5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13590" yWindow="4155" windowWidth="21660" windowHeight="14550" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="12855" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
   </bookViews>
   <sheets>
     <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>INVOICE DATE
 發票日期</t>
@@ -151,6 +151,10 @@
   </si>
   <si>
     <t>JKTL246686</t>
+  </si>
+  <si>
+    <t>VAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -706,7 +710,7 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <v>77000</v>
